--- a/dataset/construct/dataset_splits/data_size/10_percent/tum/fold2.xlsx
+++ b/dataset/construct/dataset_splits/data_size/10_percent/tum/fold2.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AN7"/>
+  <dimension ref="A1:AK7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -446,185 +446,170 @@
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
-          <t>DM</t>
+          <t>BMI</t>
         </is>
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>BMI</t>
+          <t>AFPRE</t>
         </is>
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t>CABGPRE</t>
+          <t>LVEFPRE</t>
         </is>
       </c>
       <c r="G1" s="1" t="inlineStr">
         <is>
-          <t>AFPRE</t>
+          <t>PREDILATION</t>
         </is>
       </c>
       <c r="H1" s="1" t="inlineStr">
         <is>
-          <t>LVEFPRE</t>
+          <t>CT_ValScNCC</t>
         </is>
       </c>
       <c r="I1" s="1" t="inlineStr">
         <is>
-          <t>NTPROBNPPRE</t>
+          <t>CT_ValScRCC</t>
         </is>
       </c>
       <c r="J1" s="1" t="inlineStr">
         <is>
-          <t>PREDILATION</t>
+          <t>CT_ValScLCC</t>
         </is>
       </c>
       <c r="K1" s="1" t="inlineStr">
         <is>
-          <t>CT_ValScNCC</t>
+          <t>CT_ValvScTot</t>
         </is>
       </c>
       <c r="L1" s="1" t="inlineStr">
         <is>
-          <t>CT_ValScRCC</t>
+          <t>CT_AnnScNCC</t>
         </is>
       </c>
       <c r="M1" s="1" t="inlineStr">
         <is>
-          <t>CT_ValScLCC</t>
+          <t>CT_AnnScRCC</t>
         </is>
       </c>
       <c r="N1" s="1" t="inlineStr">
         <is>
-          <t>CT_ValvScTot</t>
+          <t>CT_AnnScLCC</t>
         </is>
       </c>
       <c r="O1" s="1" t="inlineStr">
         <is>
-          <t>CT_AnnScNCC</t>
+          <t>CT_AnnScTot</t>
         </is>
       </c>
       <c r="P1" s="1" t="inlineStr">
         <is>
-          <t>CT_AnnScRCC</t>
+          <t>CT_LVOTScNCC</t>
         </is>
       </c>
       <c r="Q1" s="1" t="inlineStr">
         <is>
-          <t>CT_AnnScLCC</t>
+          <t>CT_LVOTScRCC</t>
         </is>
       </c>
       <c r="R1" s="1" t="inlineStr">
         <is>
-          <t>CT_AnnScTot</t>
+          <t>CT_LVOTScLCC</t>
         </is>
       </c>
       <c r="S1" s="1" t="inlineStr">
         <is>
-          <t>CT_LVOTScNCC</t>
+          <t>CT_LVOTScTot</t>
         </is>
       </c>
       <c r="T1" s="1" t="inlineStr">
         <is>
-          <t>CT_LVOTScRCC</t>
+          <t>SEX</t>
         </is>
       </c>
       <c r="U1" s="1" t="inlineStr">
         <is>
-          <t>CT_LVOTScLCC</t>
+          <t>CT_AnnMean</t>
         </is>
       </c>
       <c r="V1" s="1" t="inlineStr">
         <is>
-          <t>CT_LVOTScTot</t>
+          <t>ECC_INDEX</t>
         </is>
       </c>
       <c r="W1" s="1" t="inlineStr">
         <is>
-          <t>SEX</t>
+          <t>CT_Peri_Deri</t>
         </is>
       </c>
       <c r="X1" s="1" t="inlineStr">
         <is>
-          <t>CT_AnnMean</t>
+          <t>CT_Area_Deri</t>
         </is>
       </c>
       <c r="Y1" s="1" t="inlineStr">
         <is>
-          <t>ECC_INDEX</t>
+          <t>nyha2</t>
         </is>
       </c>
       <c r="Z1" s="1" t="inlineStr">
         <is>
-          <t>CT_Peri_Deri</t>
+          <t>nyha3</t>
         </is>
       </c>
       <c r="AA1" s="1" t="inlineStr">
         <is>
-          <t>CT_Area_Deri</t>
+          <t>nyha4</t>
         </is>
       </c>
       <c r="AB1" s="1" t="inlineStr">
         <is>
-          <t>nyha2</t>
+          <t>model1</t>
         </is>
       </c>
       <c r="AC1" s="1" t="inlineStr">
         <is>
-          <t>nyha3</t>
+          <t>model2</t>
         </is>
       </c>
       <c r="AD1" s="1" t="inlineStr">
         <is>
-          <t>nyha4</t>
+          <t>model3</t>
         </is>
       </c>
       <c r="AE1" s="1" t="inlineStr">
         <is>
-          <t>model1</t>
+          <t>model4</t>
         </is>
       </c>
       <c r="AF1" s="1" t="inlineStr">
         <is>
-          <t>model2</t>
+          <t>model7</t>
         </is>
       </c>
       <c r="AG1" s="1" t="inlineStr">
         <is>
-          <t>model3</t>
+          <t>model8</t>
         </is>
       </c>
       <c r="AH1" s="1" t="inlineStr">
         <is>
-          <t>model4</t>
+          <t>brand2</t>
         </is>
       </c>
       <c r="AI1" s="1" t="inlineStr">
         <is>
-          <t>model7</t>
+          <t>brand8</t>
         </is>
       </c>
       <c r="AJ1" s="1" t="inlineStr">
         <is>
-          <t>model8</t>
+          <t>QRSADM</t>
         </is>
       </c>
       <c r="AK1" s="1" t="inlineStr">
-        <is>
-          <t>brand2</t>
-        </is>
-      </c>
-      <c r="AL1" s="1" t="inlineStr">
-        <is>
-          <t>brand8</t>
-        </is>
-      </c>
-      <c r="AM1" s="1" t="inlineStr">
-        <is>
-          <t>QRSADM</t>
-        </is>
-      </c>
-      <c r="AN1" s="1" t="inlineStr">
         <is>
           <t>PQADM</t>
         </is>
@@ -632,7 +617,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>300</v>
+        <v>2419</v>
       </c>
       <c r="B2" t="inlineStr">
         <is>
@@ -640,86 +625,88 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>87.77125827059091</v>
+        <v>83.00703576951349</v>
       </c>
       <c r="D2" t="n">
-        <v>0</v>
+        <v>24.1588179685585</v>
       </c>
       <c r="E2" t="n">
-        <v>24.6913580246913</v>
+        <v>0</v>
       </c>
       <c r="F2" t="n">
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="G2" t="n">
         <v>0</v>
       </c>
       <c r="H2" t="n">
-        <v>52</v>
-      </c>
-      <c r="I2" t="inlineStr"/>
+        <v>441.3</v>
+      </c>
+      <c r="I2" t="n">
+        <v>341.5</v>
+      </c>
       <c r="J2" t="n">
-        <v>1</v>
+        <v>36.7</v>
       </c>
       <c r="K2" t="n">
-        <v>539</v>
+        <v>819.5</v>
       </c>
       <c r="L2" t="n">
-        <v>316</v>
+        <v>36.3</v>
       </c>
       <c r="M2" t="n">
-        <v>146</v>
+        <v>17.6</v>
       </c>
       <c r="N2" t="n">
-        <v>1001</v>
+        <v>9.9</v>
       </c>
       <c r="O2" t="n">
-        <v>0</v>
+        <v>63.8</v>
       </c>
       <c r="P2" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="Q2" t="n">
         <v>0</v>
       </c>
       <c r="R2" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="S2" t="n">
         <v>0</v>
       </c>
       <c r="T2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="U2" t="n">
-        <v>0</v>
+        <v>22.95</v>
       </c>
       <c r="V2" t="n">
-        <v>0</v>
+        <v>0.17</v>
       </c>
       <c r="W2" t="n">
-        <v>1</v>
+        <v>23.4275528393175</v>
       </c>
       <c r="X2" t="n">
-        <v>25.55</v>
+        <v>23.0743446333452</v>
       </c>
       <c r="Y2" t="n">
-        <v>0.128205128205128</v>
+        <v>1</v>
       </c>
       <c r="Z2" t="n">
-        <v>25.8467023172906</v>
+        <v>0</v>
       </c>
       <c r="AA2" t="n">
-        <v>25.4282983710565</v>
+        <v>0</v>
       </c>
       <c r="AB2" t="n">
         <v>0</v>
       </c>
       <c r="AC2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AD2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AE2" t="n">
         <v>0</v>
@@ -728,7 +715,7 @@
         <v>0</v>
       </c>
       <c r="AG2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AH2" t="n">
         <v>0</v>
@@ -737,24 +724,15 @@
         <v>0</v>
       </c>
       <c r="AJ2" t="n">
-        <v>0</v>
+        <v>98</v>
       </c>
       <c r="AK2" t="n">
-        <v>1</v>
-      </c>
-      <c r="AL2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM2" t="n">
-        <v>98</v>
-      </c>
-      <c r="AN2" t="n">
-        <v>190</v>
+        <v>234</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>2583</v>
+        <v>922</v>
       </c>
       <c r="B3" t="inlineStr">
         <is>
@@ -762,82 +740,82 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>85.0467322926965</v>
+        <v>75.0324815258448</v>
       </c>
       <c r="D3" t="n">
-        <v>1</v>
+        <v>26.4721074380165</v>
       </c>
       <c r="E3" t="n">
-        <v>26.2975778546712</v>
+        <v>1</v>
       </c>
       <c r="F3" t="n">
-        <v>0</v>
+        <v>60</v>
       </c>
       <c r="G3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H3" t="n">
-        <v>60</v>
+        <v>280</v>
       </c>
       <c r="I3" t="n">
-        <v>1320</v>
+        <v>391</v>
       </c>
       <c r="J3" t="n">
-        <v>1</v>
+        <v>306</v>
       </c>
       <c r="K3" t="n">
-        <v>664</v>
+        <v>977</v>
       </c>
       <c r="L3" t="n">
-        <v>401</v>
+        <v>16</v>
       </c>
       <c r="M3" t="n">
-        <v>318</v>
+        <v>31</v>
       </c>
       <c r="N3" t="n">
-        <v>1383</v>
+        <v>32</v>
       </c>
       <c r="O3" t="n">
-        <v>37</v>
+        <v>79</v>
       </c>
       <c r="P3" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="Q3" t="n">
-        <v>95</v>
+        <v>0</v>
       </c>
       <c r="R3" t="n">
-        <v>140</v>
+        <v>0</v>
       </c>
       <c r="S3" t="n">
         <v>0</v>
       </c>
       <c r="T3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="U3" t="n">
-        <v>7</v>
+        <v>26.5</v>
       </c>
       <c r="V3" t="n">
-        <v>7</v>
+        <v>0.23</v>
       </c>
       <c r="W3" t="n">
-        <v>1</v>
+        <v>27.3745861981156</v>
       </c>
       <c r="X3" t="n">
-        <v>24.65</v>
+        <v>26.7218716216114</v>
       </c>
       <c r="Y3" t="n">
-        <v>0.220216606498195</v>
+        <v>0</v>
       </c>
       <c r="Z3" t="n">
-        <v>24.8281130634072</v>
+        <v>1</v>
       </c>
       <c r="AA3" t="n">
-        <v>24.3439993862133</v>
+        <v>0</v>
       </c>
       <c r="AB3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AC3" t="n">
         <v>0</v>
@@ -846,39 +824,28 @@
         <v>0</v>
       </c>
       <c r="AE3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AF3" t="n">
         <v>0</v>
       </c>
       <c r="AG3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AH3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AI3" t="n">
         <v>0</v>
       </c>
       <c r="AJ3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM3" t="n">
-        <v>130</v>
-      </c>
-      <c r="AN3" t="n">
-        <v>154</v>
-      </c>
+        <v>86</v>
+      </c>
+      <c r="AK3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>568</v>
+        <v>714</v>
       </c>
       <c r="B4" t="inlineStr">
         <is>
@@ -886,88 +853,88 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>80.78428017339721</v>
+        <v>86.8923168428524</v>
       </c>
       <c r="D4" t="n">
-        <v>1</v>
+        <v>22.6473769605191</v>
       </c>
       <c r="E4" t="n">
-        <v>36.3321799307958</v>
+        <v>0</v>
       </c>
       <c r="F4" t="n">
-        <v>0</v>
+        <v>35</v>
       </c>
       <c r="G4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H4" t="n">
-        <v>60</v>
+        <v>648</v>
       </c>
       <c r="I4" t="n">
-        <v>225</v>
+        <v>498</v>
       </c>
       <c r="J4" t="n">
-        <v>1</v>
+        <v>649</v>
       </c>
       <c r="K4" t="n">
-        <v>229.8</v>
+        <v>1795</v>
       </c>
       <c r="L4" t="n">
-        <v>233.3</v>
+        <v>263</v>
       </c>
       <c r="M4" t="n">
-        <v>398.5</v>
+        <v>122</v>
       </c>
       <c r="N4" t="n">
-        <v>861.6</v>
+        <v>56</v>
       </c>
       <c r="O4" t="n">
-        <v>0</v>
+        <v>441</v>
       </c>
       <c r="P4" t="n">
-        <v>7.6</v>
+        <v>31</v>
       </c>
       <c r="Q4" t="n">
-        <v>46.3</v>
+        <v>68</v>
       </c>
       <c r="R4" t="n">
-        <v>53.9</v>
+        <v>6</v>
       </c>
       <c r="S4" t="n">
-        <v>0</v>
+        <v>105</v>
       </c>
       <c r="T4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="U4" t="n">
-        <v>0</v>
+        <v>25.75</v>
       </c>
       <c r="V4" t="n">
-        <v>0</v>
+        <v>0.27</v>
       </c>
       <c r="W4" t="n">
-        <v>1</v>
+        <v>25.9103641456583</v>
       </c>
       <c r="X4" t="n">
-        <v>26.15</v>
+        <v>25.3531036326332</v>
       </c>
       <c r="Y4" t="n">
-        <v>0.262458471760797</v>
+        <v>0</v>
       </c>
       <c r="Z4" t="n">
-        <v>26.8334606569901</v>
+        <v>0</v>
       </c>
       <c r="AA4" t="n">
-        <v>26.0709028381822</v>
+        <v>1</v>
       </c>
       <c r="AB4" t="n">
         <v>0</v>
       </c>
       <c r="AC4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AD4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AE4" t="n">
         <v>0</v>
@@ -979,30 +946,21 @@
         <v>0</v>
       </c>
       <c r="AH4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AI4" t="n">
         <v>0</v>
       </c>
       <c r="AJ4" t="n">
-        <v>1</v>
+        <v>118</v>
       </c>
       <c r="AK4" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL4" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM4" t="n">
-        <v>80</v>
-      </c>
-      <c r="AN4" t="n">
-        <v>204</v>
+        <v>148</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>2093</v>
+        <v>2217</v>
       </c>
       <c r="B5" t="inlineStr">
         <is>
@@ -1010,85 +968,85 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>84.1487284521003</v>
+        <v>82.77436832965751</v>
       </c>
       <c r="D5" t="n">
-        <v>0</v>
+        <v>20.6131310030261</v>
       </c>
       <c r="E5" t="n">
-        <v>29.0174471992653</v>
+        <v>0</v>
       </c>
       <c r="F5" t="n">
-        <v>0</v>
+        <v>45</v>
       </c>
       <c r="G5" t="n">
         <v>0</v>
       </c>
       <c r="H5" t="n">
-        <v>51</v>
+        <v>348.5</v>
       </c>
       <c r="I5" t="n">
-        <v>5510</v>
+        <v>31.1</v>
       </c>
       <c r="J5" t="n">
-        <v>0</v>
+        <v>139</v>
       </c>
       <c r="K5" t="n">
-        <v>489.6</v>
+        <v>518.6</v>
       </c>
       <c r="L5" t="n">
-        <v>405.5</v>
+        <v>205.1</v>
       </c>
       <c r="M5" t="n">
-        <v>217.9</v>
+        <v>0</v>
       </c>
       <c r="N5" t="n">
-        <v>1113</v>
+        <v>78.7</v>
       </c>
       <c r="O5" t="n">
-        <v>0</v>
+        <v>283.8</v>
       </c>
       <c r="P5" t="n">
-        <v>0</v>
+        <v>109.1</v>
       </c>
       <c r="Q5" t="n">
-        <v>15.1</v>
+        <v>0</v>
       </c>
       <c r="R5" t="n">
-        <v>15.1</v>
+        <v>170.5</v>
       </c>
       <c r="S5" t="n">
-        <v>0</v>
+        <v>279.6</v>
       </c>
       <c r="T5" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="U5" t="n">
-        <v>0</v>
+        <v>23.75</v>
       </c>
       <c r="V5" t="n">
-        <v>0</v>
+        <v>0.3</v>
       </c>
       <c r="W5" t="n">
-        <v>2</v>
+        <v>24.0005092946269</v>
       </c>
       <c r="X5" t="n">
-        <v>23.95</v>
+        <v>23.39481796886</v>
       </c>
       <c r="Y5" t="n">
-        <v>0.353951890034364</v>
+        <v>0</v>
       </c>
       <c r="Z5" t="n">
-        <v>23.9686783804431</v>
+        <v>1</v>
       </c>
       <c r="AA5" t="n">
-        <v>22.9720679092787</v>
+        <v>0</v>
       </c>
       <c r="AB5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AC5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AD5" t="n">
         <v>0</v>
@@ -1097,7 +1055,7 @@
         <v>0</v>
       </c>
       <c r="AF5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AG5" t="n">
         <v>0</v>
@@ -1109,24 +1067,15 @@
         <v>0</v>
       </c>
       <c r="AJ5" t="n">
-        <v>0</v>
+        <v>158</v>
       </c>
       <c r="AK5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM5" t="n">
-        <v>108</v>
-      </c>
-      <c r="AN5" t="n">
-        <v>204</v>
+        <v>254</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>555</v>
+        <v>2886</v>
       </c>
       <c r="B6" t="inlineStr">
         <is>
@@ -1134,79 +1083,79 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>82.8866092478516</v>
+        <v>87.4232017960808</v>
       </c>
       <c r="D6" t="n">
-        <v>0</v>
+        <v>31.3145661157024</v>
       </c>
       <c r="E6" t="n">
-        <v>26.4235698242832</v>
+        <v>0</v>
       </c>
       <c r="F6" t="n">
-        <v>0</v>
+        <v>60</v>
       </c>
       <c r="G6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H6" t="n">
-        <v>36</v>
+        <v>569</v>
       </c>
       <c r="I6" t="n">
-        <v>1160</v>
+        <v>741</v>
       </c>
       <c r="J6" t="n">
-        <v>1</v>
+        <v>592</v>
       </c>
       <c r="K6" t="n">
-        <v>236</v>
+        <v>1902</v>
       </c>
       <c r="L6" t="n">
-        <v>300</v>
+        <v>261</v>
       </c>
       <c r="M6" t="n">
-        <v>165</v>
+        <v>29</v>
       </c>
       <c r="N6" t="n">
-        <v>701</v>
+        <v>100</v>
       </c>
       <c r="O6" t="n">
-        <v>16</v>
+        <v>390</v>
       </c>
       <c r="P6" t="n">
-        <v>10</v>
+        <v>93</v>
       </c>
       <c r="Q6" t="n">
-        <v>29</v>
+        <v>0</v>
       </c>
       <c r="R6" t="n">
-        <v>55</v>
+        <v>0</v>
       </c>
       <c r="S6" t="n">
-        <v>0</v>
+        <v>93</v>
       </c>
       <c r="T6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="U6" t="n">
-        <v>26</v>
+        <v>24.35</v>
       </c>
       <c r="V6" t="n">
-        <v>26</v>
+        <v>0.2</v>
       </c>
       <c r="W6" t="n">
-        <v>1</v>
+        <v>23.9686783804431</v>
       </c>
       <c r="X6" t="n">
-        <v>23.3</v>
+        <v>23.3675988578761</v>
       </c>
       <c r="Y6" t="n">
-        <v>0.158102766798419</v>
+        <v>0</v>
       </c>
       <c r="Z6" t="n">
-        <v>23.2365673542144</v>
+        <v>1</v>
       </c>
       <c r="AA6" t="n">
-        <v>23.1211849536588</v>
+        <v>0</v>
       </c>
       <c r="AB6" t="n">
         <v>0</v>
@@ -1215,13 +1164,13 @@
         <v>0</v>
       </c>
       <c r="AD6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AE6" t="n">
         <v>0</v>
       </c>
       <c r="AF6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AG6" t="n">
         <v>0</v>
@@ -1233,24 +1182,15 @@
         <v>0</v>
       </c>
       <c r="AJ6" t="n">
-        <v>0</v>
+        <v>130</v>
       </c>
       <c r="AK6" t="n">
-        <v>1</v>
-      </c>
-      <c r="AL6" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM6" t="n">
-        <v>75</v>
-      </c>
-      <c r="AN6" t="n">
-        <v>170</v>
+        <v>212</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>645</v>
+        <v>688</v>
       </c>
       <c r="B7" t="inlineStr">
         <is>
@@ -1258,85 +1198,85 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>85.26030306487181</v>
+        <v>86.5826564757776</v>
       </c>
       <c r="D7" t="n">
-        <v>0</v>
+        <v>28.7639710716633</v>
       </c>
       <c r="E7" t="n">
-        <v>23.2334561768947</v>
+        <v>0</v>
       </c>
       <c r="F7" t="n">
-        <v>0</v>
+        <v>60</v>
       </c>
       <c r="G7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H7" t="n">
-        <v>60</v>
+        <v>480</v>
       </c>
       <c r="I7" t="n">
-        <v>196</v>
+        <v>240.2</v>
       </c>
       <c r="J7" t="n">
-        <v>1</v>
+        <v>281.9</v>
       </c>
       <c r="K7" t="n">
-        <v>114</v>
+        <v>1002.1</v>
       </c>
       <c r="L7" t="n">
-        <v>145</v>
+        <v>46.7</v>
       </c>
       <c r="M7" t="n">
-        <v>130</v>
+        <v>21</v>
       </c>
       <c r="N7" t="n">
-        <v>389</v>
+        <v>37.1</v>
       </c>
       <c r="O7" t="n">
-        <v>0</v>
+        <v>104.8</v>
       </c>
       <c r="P7" t="n">
         <v>0</v>
       </c>
       <c r="Q7" t="n">
-        <v>42</v>
+        <v>0</v>
       </c>
       <c r="R7" t="n">
-        <v>42</v>
+        <v>0</v>
       </c>
       <c r="S7" t="n">
         <v>0</v>
       </c>
       <c r="T7" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="U7" t="n">
-        <v>42</v>
+        <v>22.25</v>
       </c>
       <c r="V7" t="n">
-        <v>42</v>
+        <v>0.18</v>
       </c>
       <c r="W7" t="n">
-        <v>2</v>
+        <v>22.2498090145149</v>
       </c>
       <c r="X7" t="n">
-        <v>21.4</v>
+        <v>22.0244421422418</v>
       </c>
       <c r="Y7" t="n">
-        <v>0.238683127572017</v>
+        <v>1</v>
       </c>
       <c r="Z7" t="n">
-        <v>21.6450216450216</v>
+        <v>0</v>
       </c>
       <c r="AA7" t="n">
-        <v>21.2868030290747</v>
+        <v>0</v>
       </c>
       <c r="AB7" t="n">
         <v>0</v>
       </c>
       <c r="AC7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AD7" t="n">
         <v>0</v>
@@ -1345,7 +1285,7 @@
         <v>0</v>
       </c>
       <c r="AF7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AG7" t="n">
         <v>0</v>
@@ -1357,19 +1297,10 @@
         <v>0</v>
       </c>
       <c r="AJ7" t="n">
-        <v>0</v>
+        <v>84</v>
       </c>
       <c r="AK7" t="n">
-        <v>1</v>
-      </c>
-      <c r="AL7" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM7" t="n">
-        <v>72</v>
-      </c>
-      <c r="AN7" t="n">
-        <v>238</v>
+        <v>154</v>
       </c>
     </row>
   </sheetData>
